--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484114_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484114_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.5085</v>
+        <v>5.0685</v>
       </c>
       <c r="E2" t="n">
-        <v>8.0273</v>
+        <v>6.5592</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.5188</v>
+        <v>-1.4908</v>
       </c>
       <c r="G2" t="n">
         <v>5.4168</v>
@@ -610,13 +610,13 @@
         <v>1.5871</v>
       </c>
       <c r="S2" t="n">
-        <v>1.895</v>
+        <v>0.4549</v>
       </c>
       <c r="T2" t="n">
-        <v>2.0294</v>
+        <v>0.5613</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.1344</v>
+        <v>-0.1064</v>
       </c>
       <c r="V2" t="n">
         <v>-1.3984</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.9237</v>
+        <v>2.736</v>
       </c>
       <c r="E3" t="n">
-        <v>3.1582</v>
+        <v>2.9144</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.2345</v>
+        <v>-0.1784</v>
       </c>
       <c r="G3" t="n">
         <v>0.8987000000000001</v>
@@ -688,13 +688,13 @@
         <v>2.3806</v>
       </c>
       <c r="S3" t="n">
-        <v>0.6893</v>
+        <v>0.5017</v>
       </c>
       <c r="T3" t="n">
-        <v>0.9411</v>
+        <v>0.6973</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.2518</v>
+        <v>-0.1957</v>
       </c>
       <c r="V3" t="n">
         <v>0.1453</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>L. NDIAYE</t>
+          <t>L. MARTINEZ YRANZO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.3822</v>
+        <v>1.1457</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1782</v>
+        <v>0.728</v>
       </c>
       <c r="F4" t="n">
-        <v>1.204</v>
+        <v>0.4177</v>
       </c>
       <c r="G4" t="n">
-        <v>-2.0897</v>
+        <v>0.2297</v>
       </c>
       <c r="H4" t="n">
-        <v>-2.4642</v>
+        <v>1.0329</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3745</v>
+        <v>-0.8032</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.9093</v>
+        <v>0.4085</v>
       </c>
       <c r="K4" t="n">
-        <v>-1.6724</v>
+        <v>1.0887</v>
       </c>
       <c r="L4" t="n">
-        <v>0.7631</v>
+        <v>-0.6802</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.1804</v>
+        <v>-0.1788</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.7917999999999999</v>
+        <v>-0.0558</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.3886</v>
+        <v>-0.123</v>
       </c>
       <c r="P4" t="n">
-        <v>1.3887</v>
+        <v>0.7935</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.1984</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.5871</v>
+        <v>0.7935</v>
       </c>
       <c r="S4" t="n">
-        <v>0.8768</v>
+        <v>-0.0723</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0794</v>
+        <v>0.1248</v>
       </c>
       <c r="U4" t="n">
-        <v>0.7974</v>
+        <v>-0.197</v>
       </c>
       <c r="V4" t="n">
-        <v>1.2065</v>
+        <v>0.1947</v>
       </c>
       <c r="W4" t="n">
-        <v>1.2065</v>
+        <v>0.1947</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>L. MARTINEZ YRANZO</t>
+          <t>L. NDIAYE</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.6177</v>
+        <v>0.8951</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1158</v>
+        <v>0.2802</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5018</v>
+        <v>0.6149</v>
       </c>
       <c r="G5" t="n">
-        <v>0.2297</v>
+        <v>-2.0897</v>
       </c>
       <c r="H5" t="n">
-        <v>1.0329</v>
+        <v>-2.4642</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.8032</v>
+        <v>0.3745</v>
       </c>
       <c r="J5" t="n">
-        <v>0.4085</v>
+        <v>-0.9093</v>
       </c>
       <c r="K5" t="n">
-        <v>1.0887</v>
+        <v>-1.6724</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.6802</v>
+        <v>0.7631</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.1788</v>
+        <v>-1.1804</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.0558</v>
+        <v>-0.7917999999999999</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.123</v>
+        <v>-0.3886</v>
       </c>
       <c r="P5" t="n">
-        <v>0.7935</v>
+        <v>1.3887</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-0.1984</v>
       </c>
       <c r="R5" t="n">
-        <v>0.7935</v>
+        <v>1.5871</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.6002999999999999</v>
+        <v>0.3897</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.4874</v>
+        <v>0.1815</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1129</v>
+        <v>0.2082</v>
       </c>
       <c r="V5" t="n">
-        <v>0.1947</v>
+        <v>1.2065</v>
       </c>
       <c r="W5" t="n">
-        <v>0.1947</v>
+        <v>1.2065</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4002</v>
+        <v>0.4549</v>
       </c>
       <c r="E6" t="n">
-        <v>3.8403</v>
+        <v>3.6986</v>
       </c>
       <c r="F6" t="n">
-        <v>-3.4401</v>
+        <v>-3.2438</v>
       </c>
       <c r="G6" t="n">
         <v>3.0502</v>
@@ -922,13 +922,13 @@
         <v>1.7855</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.2714</v>
+        <v>-0.2168</v>
       </c>
       <c r="T6" t="n">
-        <v>0.3742</v>
+        <v>0.2325</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.6457000000000001</v>
+        <v>-0.4493</v>
       </c>
       <c r="V6" t="n">
         <v>-0.9899</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.463</v>
+        <v>-0.4069</v>
       </c>
       <c r="E7" t="n">
         <v>-0.1669</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.2962</v>
+        <v>-0.2401</v>
       </c>
       <c r="G7" t="n">
         <v>0.0202</v>
@@ -1000,13 +1000,13 @@
         <v>0.1984</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.1496</v>
+        <v>-0.0935</v>
       </c>
       <c r="T7" t="n">
         <v>-0.187</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0374</v>
+        <v>0.0935</v>
       </c>
       <c r="V7" t="n">
         <v>-0.532</v>
@@ -1033,10 +1033,10 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.2228</v>
+        <v>-1.3646</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.4808</v>
+        <v>-0.6225000000000001</v>
       </c>
       <c r="F8" t="n">
         <v>-0.7421</v>
@@ -1078,10 +1078,10 @@
         <v>0.1984</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0227</v>
+        <v>-0.119</v>
       </c>
       <c r="T8" t="n">
-        <v>0.1191</v>
+        <v>-0.0226</v>
       </c>
       <c r="U8" t="n">
         <v>-0.0964</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-4.2508</v>
+        <v>-4.1386</v>
       </c>
       <c r="E9" t="n">
         <v>-0.5669999999999999</v>
       </c>
       <c r="F9" t="n">
-        <v>-3.6838</v>
+        <v>-3.5716</v>
       </c>
       <c r="G9" t="n">
         <v>-1.4172</v>
@@ -1156,13 +1156,13 @@
         <v>0.9919</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.611</v>
+        <v>-0.4988</v>
       </c>
       <c r="T9" t="n">
         <v>0.1304</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.7413999999999999</v>
+        <v>-0.6292</v>
       </c>
       <c r="V9" t="n">
         <v>-3.0162</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-5.5023</v>
+        <v>-4.6759</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.6171</v>
+        <v>-1.9028</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.8853</v>
+        <v>-2.7731</v>
       </c>
       <c r="G10" t="n">
         <v>-4.1141</v>
@@ -1234,13 +1234,13 @@
         <v>2.3806</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.4272</v>
+        <v>-0.6008</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.8047</v>
+        <v>-0.0905</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.6225000000000001</v>
+        <v>-0.5103</v>
       </c>
       <c r="V10" t="n">
         <v>-2.3417</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-6.0022</v>
+        <v>-5.0114</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.0958</v>
+        <v>-3.2172</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.9064</v>
+        <v>-1.7942</v>
       </c>
       <c r="G11" t="n">
         <v>-2.4438</v>
@@ -1312,13 +1312,13 @@
         <v>1.9838</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.5009</v>
+        <v>-0.5101</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.9748</v>
+        <v>-0.09619999999999999</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.5261</v>
+        <v>-0.4139</v>
       </c>
       <c r="V11" t="n">
         <v>-1.8591</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.6088</v>
+        <v>-5.297199999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>7.392200000000002</v>
+        <v>7.703999999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>-13.0014</v>
+        <v>-13.0015</v>
       </c>
       <c r="G12" t="n">
         <v>-1.5065</v>
@@ -1390,13 +1390,13 @@
         <v>13.8869</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.0766</v>
+        <v>-0.765</v>
       </c>
       <c r="T12" t="n">
-        <v>1.2197</v>
+        <v>1.5315</v>
       </c>
       <c r="U12" t="n">
-        <v>-2.2964</v>
+        <v>-2.2965</v>
       </c>
       <c r="V12" t="n">
         <v>-8.977399999999999</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>8.092499999999999</v>
+        <v>7.0816</v>
       </c>
       <c r="E13" t="n">
-        <v>8.4781</v>
+        <v>7.5598</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.3855</v>
+        <v>-0.4782</v>
       </c>
       <c r="G13" t="n">
         <v>1.388</v>
@@ -1468,13 +1468,13 @@
         <v>1.1903</v>
       </c>
       <c r="S13" t="n">
-        <v>1.4856</v>
+        <v>0.4747</v>
       </c>
       <c r="T13" t="n">
-        <v>1.1168</v>
+        <v>0.1985</v>
       </c>
       <c r="U13" t="n">
-        <v>0.3688</v>
+        <v>0.2762</v>
       </c>
       <c r="V13" t="n">
         <v>5.0206</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.9817</v>
+        <v>3.8982</v>
       </c>
       <c r="E14" t="n">
-        <v>3.5609</v>
+        <v>4.173</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.5792</v>
+        <v>-0.2748</v>
       </c>
       <c r="G14" t="n">
         <v>2.9432</v>
@@ -1546,13 +1546,13 @@
         <v>0.7935</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.755</v>
+        <v>0.1615</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.3627</v>
+        <v>0.2495</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.3923</v>
+        <v>-0.08790000000000001</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.5138</v>
+        <v>2.1755</v>
       </c>
       <c r="E15" t="n">
-        <v>3.0912</v>
+        <v>2.7851</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.5773</v>
+        <v>-0.6096</v>
       </c>
       <c r="G15" t="n">
         <v>1.1326</v>
@@ -1624,13 +1624,13 @@
         <v>0.7935</v>
       </c>
       <c r="S15" t="n">
-        <v>0.2505</v>
+        <v>-0.08790000000000001</v>
       </c>
       <c r="T15" t="n">
-        <v>0.2438</v>
+        <v>-0.0623</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0067</v>
+        <v>-0.0256</v>
       </c>
       <c r="V15" t="n">
         <v>0.3373</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.0809</v>
+        <v>2.0511</v>
       </c>
       <c r="E16" t="n">
-        <v>1.9169</v>
+        <v>1.6108</v>
       </c>
       <c r="F16" t="n">
-        <v>0.164</v>
+        <v>0.4403</v>
       </c>
       <c r="G16" t="n">
         <v>-0.0515</v>
@@ -1702,13 +1702,13 @@
         <v>0.3968</v>
       </c>
       <c r="S16" t="n">
-        <v>0.3146</v>
+        <v>0.2848</v>
       </c>
       <c r="T16" t="n">
-        <v>0.4932</v>
+        <v>0.1871</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.1786</v>
+        <v>0.0978</v>
       </c>
       <c r="V16" t="n">
         <v>2.4129</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.2956</v>
+        <v>1.7701</v>
       </c>
       <c r="E17" t="n">
-        <v>0.0974</v>
+        <v>0.4035</v>
       </c>
       <c r="F17" t="n">
-        <v>1.1982</v>
+        <v>1.3665</v>
       </c>
       <c r="G17" t="n">
         <v>2.1244</v>
@@ -1780,13 +1780,13 @@
         <v>1.1903</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.0352</v>
+        <v>0.4393</v>
       </c>
       <c r="T17" t="n">
-        <v>0.0794</v>
+        <v>0.3855</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1146</v>
+        <v>0.0537</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.1177</v>
+        <v>0.8456</v>
       </c>
       <c r="E18" t="n">
-        <v>1.8909</v>
+        <v>1.4828</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.7732</v>
+        <v>-0.6372</v>
       </c>
       <c r="G18" t="n">
         <v>0.6359</v>
@@ -1858,13 +1858,13 @@
         <v>0.3968</v>
       </c>
       <c r="S18" t="n">
-        <v>1.077</v>
+        <v>0.8048999999999999</v>
       </c>
       <c r="T18" t="n">
-        <v>0.9977</v>
+        <v>0.5896</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0793</v>
+        <v>0.2153</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.3385</v>
+        <v>0.2747</v>
       </c>
       <c r="E19" t="n">
-        <v>1.9299</v>
+        <v>1.7259</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.5914</v>
+        <v>-1.4511</v>
       </c>
       <c r="G19" t="n">
         <v>0.5199</v>
@@ -1936,13 +1936,13 @@
         <v>0.1984</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.0425</v>
+        <v>-0.1063</v>
       </c>
       <c r="T19" t="n">
-        <v>0.3685</v>
+        <v>0.1644</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.411</v>
+        <v>-0.2707</v>
       </c>
       <c r="V19" t="n">
         <v>-0.3373</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.3964</v>
+        <v>-1.5997</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.4847</v>
+        <v>-1.0765</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.9117</v>
+        <v>-0.5232</v>
       </c>
       <c r="G20" t="n">
         <v>1.0912</v>
@@ -2014,13 +2014,13 @@
         <v>0.3968</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.9086</v>
+        <v>-0.112</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.3004</v>
+        <v>0.1077</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.6083</v>
+        <v>-0.2197</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>N. BAQUES GARCIA</t>
+          <t>D. FONT RODRIGUEZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.4433</v>
+        <v>-2.5025</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.0217</v>
+        <v>-0.179</v>
       </c>
       <c r="F21" t="n">
-        <v>0.5784</v>
+        <v>-2.3235</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.5251</v>
+        <v>-3.6362</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.7659</v>
+        <v>-0.8572</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.7592</v>
+        <v>-2.779</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.4509</v>
+        <v>-1.0017</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.5312</v>
+        <v>0.469</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0803</v>
+        <v>-1.4707</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.0742</v>
+        <v>-2.6346</v>
       </c>
       <c r="N21" t="n">
-        <v>0.7653</v>
+        <v>-1.3262</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.8395</v>
+        <v>-1.3084</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.1903</v>
+        <v>-0.9919</v>
       </c>
       <c r="Q21" t="n">
         <v>-1.9838</v>
       </c>
       <c r="R21" t="n">
-        <v>0.7935</v>
+        <v>0.9919</v>
       </c>
       <c r="S21" t="n">
-        <v>0.7402</v>
+        <v>0.316</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.1189</v>
+        <v>0.4649</v>
       </c>
       <c r="U21" t="n">
-        <v>0.8591</v>
+        <v>-0.1489</v>
       </c>
       <c r="V21" t="n">
-        <v>0.532</v>
+        <v>1.8097</v>
       </c>
       <c r="W21" t="n">
-        <v>0.532</v>
+        <v>2.3417</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-0.532</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>D. FONT RODRIGUEZ</t>
+          <t>N. BAQUES GARCIA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.4505</v>
+        <v>-2.8123</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.9952</v>
+        <v>-3.0217</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.4553</v>
+        <v>0.2095</v>
       </c>
       <c r="G22" t="n">
-        <v>-3.6362</v>
+        <v>-2.5251</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.8572</v>
+        <v>-0.7659</v>
       </c>
       <c r="I22" t="n">
-        <v>-2.779</v>
+        <v>-1.7592</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.0017</v>
+        <v>-1.4509</v>
       </c>
       <c r="K22" t="n">
-        <v>0.469</v>
+        <v>-1.5312</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.4707</v>
+        <v>0.0803</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.6346</v>
+        <v>-1.0742</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.3262</v>
+        <v>0.7653</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.3084</v>
+        <v>-1.8395</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.9919</v>
+        <v>-1.1903</v>
       </c>
       <c r="Q22" t="n">
         <v>-1.9838</v>
       </c>
       <c r="R22" t="n">
-        <v>0.9919</v>
+        <v>0.7935</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.6321</v>
+        <v>0.3712</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.3514</v>
+        <v>-0.1189</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2807</v>
+        <v>0.4901</v>
       </c>
       <c r="V22" t="n">
-        <v>1.8097</v>
+        <v>0.532</v>
       </c>
       <c r="W22" t="n">
-        <v>2.3417</v>
+        <v>0.532</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.532</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.5217</v>
+        <v>-4.2131</v>
       </c>
       <c r="E23" t="n">
         <v>-2.4624</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.0593</v>
+        <v>-1.7507</v>
       </c>
       <c r="G23" t="n">
         <v>-2.1157</v>
@@ -2248,13 +2248,13 @@
         <v>0.7935</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.4177</v>
+        <v>-0.1091</v>
       </c>
       <c r="T23" t="n">
         <v>0.1304</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.5481</v>
+        <v>-0.2395</v>
       </c>
       <c r="V23" t="n">
         <v>-0.7979000000000001</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>5.6088</v>
+        <v>6.9692</v>
       </c>
       <c r="E24" t="n">
         <v>13.0013</v>
       </c>
       <c r="F24" t="n">
-        <v>-7.392300000000001</v>
+        <v>-6.032</v>
       </c>
       <c r="G24" t="n">
         <v>1.506699999999999</v>
@@ -2305,7 +2305,7 @@
         <v>10.2866</v>
       </c>
       <c r="L24" t="n">
-        <v>2.525700000000001</v>
+        <v>2.5257</v>
       </c>
       <c r="M24" t="n">
         <v>-11.3057</v>
@@ -2326,13 +2326,13 @@
         <v>7.9353</v>
       </c>
       <c r="S24" t="n">
-        <v>1.0768</v>
+        <v>2.4371</v>
       </c>
       <c r="T24" t="n">
         <v>2.2964</v>
       </c>
       <c r="U24" t="n">
-        <v>-1.2197</v>
+        <v>0.1408</v>
       </c>
       <c r="V24" t="n">
         <v>8.9773</v>
